--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.859493899511849</v>
+        <v>1.439667758670675</v>
       </c>
       <c r="D2" t="n">
-        <v>9.134419599145986</v>
+        <v>1.484343184861223</v>
       </c>
       <c r="E2" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F2" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.79012975216085</v>
+        <v>9.065896084726139</v>
       </c>
       <c r="D3" t="n">
-        <v>56.71093880451838</v>
+        <v>9.215527555734237</v>
       </c>
       <c r="E3" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F3" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.91684950351239</v>
+        <v>2.748988044320763</v>
       </c>
       <c r="D4" t="n">
-        <v>17.53974646000834</v>
+        <v>2.850208799751356</v>
       </c>
       <c r="E4" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F4" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.14156201240937</v>
+        <v>2.785503827016522</v>
       </c>
       <c r="D5" t="n">
-        <v>17.80873219253602</v>
+        <v>2.893918981287103</v>
       </c>
       <c r="E5" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F5" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.870352802365043</v>
+        <v>1.11643233038432</v>
       </c>
       <c r="D6" t="n">
-        <v>3.253666892834868</v>
+        <v>0.528720870085666</v>
       </c>
       <c r="E6" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F6" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.18045519681266</v>
+        <v>8.641823969482058</v>
       </c>
       <c r="D7" t="n">
-        <v>51.98217109202648</v>
+        <v>8.447102802454303</v>
       </c>
       <c r="E7" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F7" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.3796466194846</v>
+        <v>4.774192575666247</v>
       </c>
       <c r="D8" t="n">
-        <v>27.83214036300696</v>
+        <v>4.522722808988632</v>
       </c>
       <c r="E8" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F8" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.43210427056234</v>
+        <v>4.13271694396638</v>
       </c>
       <c r="D9" t="n">
-        <v>23.96683998105476</v>
+        <v>3.894611496921398</v>
       </c>
       <c r="E9" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F9" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.4391665396555</v>
+        <v>2.18386456269402</v>
       </c>
       <c r="D10" t="n">
-        <v>2.622160118599961</v>
+        <v>0.4261010192724936</v>
       </c>
       <c r="E10" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F10" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.394343194124436</v>
+        <v>0.8765807690452209</v>
       </c>
       <c r="D11" t="n">
-        <v>7.718271439866495</v>
+        <v>1.254219108978305</v>
       </c>
       <c r="E11" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F11" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.34505227598007</v>
+        <v>2.818570994846762</v>
       </c>
       <c r="D12" t="n">
-        <v>16.81721708764348</v>
+        <v>2.732797776742066</v>
       </c>
       <c r="E12" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F12" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>17.01493747586246</v>
+        <v>2.764927339827649</v>
       </c>
       <c r="D13" t="n">
-        <v>20.25245146737737</v>
+        <v>3.291023363448822</v>
       </c>
       <c r="E13" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F13" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.95981649862278</v>
+        <v>7.305970181026201</v>
       </c>
       <c r="D14" t="n">
-        <v>43.51278787878711</v>
+        <v>7.070828030302906</v>
       </c>
       <c r="E14" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F14" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.30718372374416</v>
+        <v>2.812417355108426</v>
       </c>
       <c r="D15" t="n">
-        <v>15.71968804831368</v>
+        <v>2.554449307850973</v>
       </c>
       <c r="E15" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F15" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.91865582406975</v>
+        <v>5.349281571411334</v>
       </c>
       <c r="D16" t="n">
-        <v>12.54158856646919</v>
+        <v>2.038008142051244</v>
       </c>
       <c r="E16" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F16" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.94345439379178</v>
+        <v>6.490811338991164</v>
       </c>
       <c r="D17" t="n">
-        <v>24.33064403659989</v>
+        <v>3.953729655947482</v>
       </c>
       <c r="E17" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F17" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>50.60747054736738</v>
+        <v>8.223713963947199</v>
       </c>
       <c r="D18" t="n">
-        <v>17.56664800758023</v>
+        <v>2.854580301231787</v>
       </c>
       <c r="E18" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F18" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>34.33806003094739</v>
+        <v>5.579934755028951</v>
       </c>
       <c r="D19" t="n">
-        <v>8.199750165570766</v>
+        <v>1.33245940190525</v>
       </c>
       <c r="E19" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F19" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.81567460940141</v>
+        <v>4.845047124027729</v>
       </c>
       <c r="D20" t="n">
-        <v>18.2934632920309</v>
+        <v>2.972687784955022</v>
       </c>
       <c r="E20" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F20" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>19.32084385790609</v>
+        <v>3.139637126909739</v>
       </c>
       <c r="D21" t="n">
-        <v>23.70852665416202</v>
+        <v>3.852635581301329</v>
       </c>
       <c r="E21" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F21" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.742008134136</v>
+        <v>4.995576321797101</v>
       </c>
       <c r="D22" t="n">
-        <v>2.63633975564347</v>
+        <v>0.4284052102920639</v>
       </c>
       <c r="E22" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F22" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>15.19274624306346</v>
+        <v>2.468821264497811</v>
       </c>
       <c r="D23" t="n">
-        <v>17.99992006155088</v>
+        <v>2.924987010002019</v>
       </c>
       <c r="E23" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F23" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>8.265323354361296</v>
+        <v>1.343115045083711</v>
       </c>
       <c r="D24" t="n">
-        <v>31.64006619602571</v>
+        <v>5.141510756854178</v>
       </c>
       <c r="E24" t="n">
-        <v>14.83149617115274</v>
+        <v>2.410118127812321</v>
       </c>
       <c r="F24" t="n">
-        <v>14.08413092763557</v>
+        <v>2.288671275740779</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
